--- a/keel_vessel_import_template.xlsx
+++ b/keel_vessel_import_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF35E44-F3EE-4A3C-80B1-577FA58F6FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8EA0D37-994B-43A7-9CBC-131640DEB7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vessels" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
   <si>
     <t>Vessel Name</t>
   </si>
@@ -46,6 +46,21 @@
     <t>Vessel Type</t>
   </si>
   <si>
+    <t>Master Email (Optional)</t>
+  </si>
+  <si>
+    <t>CTO Deck Email (Optional)</t>
+  </si>
+  <si>
+    <t>CTO Engine Email (Optional)</t>
+  </si>
+  <si>
+    <t>CTO ETO Email (Optional)</t>
+  </si>
+  <si>
+    <t>CTO Catering Email (Optional)</t>
+  </si>
+  <si>
     <t>ABS (American Bureau of Shipping)</t>
   </si>
   <si>
@@ -118,61 +133,61 @@
     <t>Platform Support Vessel</t>
   </si>
   <si>
+    <t>Ocean Pioneer</t>
+  </si>
+  <si>
     <t>Singapore</t>
   </si>
   <si>
+    <t>Global Trader</t>
+  </si>
+  <si>
     <t>Panama</t>
   </si>
   <si>
+    <t>Energy Star</t>
+  </si>
+  <si>
     <t>Marshall Islands</t>
   </si>
   <si>
+    <t>Pacific Horizon</t>
+  </si>
+  <si>
     <t>Liberia</t>
   </si>
   <si>
+    <t>Chemical Explorer</t>
+  </si>
+  <si>
     <t>Hong Kong</t>
   </si>
   <si>
+    <t>Atlantic Bridge</t>
+  </si>
+  <si>
+    <t>Auto Prestige</t>
+  </si>
+  <si>
     <t>Japan</t>
   </si>
   <si>
+    <t>Deep Diver</t>
+  </si>
+  <si>
     <t>Norway</t>
   </si>
   <si>
+    <t>India Victory</t>
+  </si>
+  <si>
     <t>India</t>
   </si>
   <si>
+    <t>Nordic Spirit</t>
+  </si>
+  <si>
     <t>Bahamas</t>
-  </si>
-  <si>
-    <t>Ocean Pioneer</t>
-  </si>
-  <si>
-    <t>Global Trader</t>
-  </si>
-  <si>
-    <t>Energy Star</t>
-  </si>
-  <si>
-    <t>Pacific Horizon</t>
-  </si>
-  <si>
-    <t>Chemical Explorer</t>
-  </si>
-  <si>
-    <t>Atlantic Bridge</t>
-  </si>
-  <si>
-    <t>Auto Prestige</t>
-  </si>
-  <si>
-    <t>Deep Diver</t>
-  </si>
-  <si>
-    <t>India Victory</t>
-  </si>
-  <si>
-    <t>Nordic Spirit</t>
   </si>
 </sst>
 </file>
@@ -561,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -569,9 +584,10 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,76 +603,171 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>9123456</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="F2" t="str">
+        <f>"master."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
+        <v>master.ocpi@keel.com</v>
+      </c>
+      <c r="G2" t="str">
+        <f>"ctodeck."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctodeck.ocpi@keel.com</v>
+      </c>
+      <c r="H2" t="str">
+        <f>"ctoeng."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctoeng.ocpi@keel.com</v>
+      </c>
+      <c r="I2" t="str">
+        <f>"ctoeto."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctoeto.ocpi@keel.com</v>
+      </c>
+      <c r="J2" t="str">
+        <f>"ctocat."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctocat.ocpi@keel.com</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>9234567</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F11" si="0">"master."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
+        <v>master.gltr@keel.com</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G11" si="1">"ctodeck."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctodeck.gltr@keel.com</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H11" si="2">"ctoeng."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctoeng.gltr@keel.com</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I11" si="3">"ctoeto."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctoeto.gltr@keel.com</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J11" si="4">"ctocat."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
+        <v>ctocat.gltr@keel.com</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>9345678</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>master.enst@keel.com</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.enst@keel.com</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.enst@keel.com</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.enst@keel.com</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.enst@keel.com</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>9456789</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>master.paho@keel.com</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.paho@keel.com</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.paho@keel.com</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.paho@keel.com</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.paho@keel.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -664,98 +775,218 @@
         <v>9567890</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>master.chex@keel.com</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.chex@keel.com</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.chex@keel.com</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.chex@keel.com</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.chex@keel.com</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>9678901</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>master.atbr@keel.com</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.atbr@keel.com</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.atbr@keel.com</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.atbr@keel.com</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.atbr@keel.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>9789012</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>master.aupr@keel.com</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.aupr@keel.com</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.aupr@keel.com</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.aupr@keel.com</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.aupr@keel.com</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>9890123</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>master.dedi@keel.com</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.dedi@keel.com</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.dedi@keel.com</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.dedi@keel.com</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.dedi@keel.com</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>9112233</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>master.invi@keel.com</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.invi@keel.com</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.invi@keel.com</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.invi@keel.com</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.invi@keel.com</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B11">
         <v>9223344</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>master.nosp@keel.com</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v>ctodeck.nosp@keel.com</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>ctoeng.nosp@keel.com</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="3"/>
+        <v>ctoeto.nosp@keel.com</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="4"/>
+        <v>ctocat.nosp@keel.com</v>
       </c>
     </row>
   </sheetData>
@@ -764,17 +995,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Class" error="Please select a valid Classification Society from the list." xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select a valid Classification Society from the provided list." xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>Reference!$A$1:$A$12</xm:f>
+            <xm:f>Reference!$A$1:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D999</xm:sqref>
+          <xm:sqref>D2:D1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Type" error="Please select a valid Vessel Type from the list." xr:uid="{00000000-0002-0000-0000-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select a valid Vessel Type from the provided list." xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>Reference!$B$1:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E999</xm:sqref>
+          <xm:sqref>E2:E1000</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -784,103 +1015,108 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/keel_vessel_import_template.xlsx
+++ b/keel_vessel_import_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8EA0D37-994B-43A7-9CBC-131640DEB7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B410AAF7-4E46-4304-B290-546768342511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vessels" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="122">
   <si>
     <t>Vessel Name</t>
   </si>
@@ -46,21 +46,6 @@
     <t>Vessel Type</t>
   </si>
   <si>
-    <t>Master Email (Optional)</t>
-  </si>
-  <si>
-    <t>CTO Deck Email (Optional)</t>
-  </si>
-  <si>
-    <t>CTO Engine Email (Optional)</t>
-  </si>
-  <si>
-    <t>CTO ETO Email (Optional)</t>
-  </si>
-  <si>
-    <t>CTO Catering Email (Optional)</t>
-  </si>
-  <si>
     <t>ABS (American Bureau of Shipping)</t>
   </si>
   <si>
@@ -133,61 +118,283 @@
     <t>Platform Support Vessel</t>
   </si>
   <si>
-    <t>Ocean Pioneer</t>
-  </si>
-  <si>
-    <t>Singapore</t>
-  </si>
-  <si>
-    <t>Global Trader</t>
+    <t>Berge Everest</t>
+  </si>
+  <si>
+    <t>Berge Aconcagua</t>
+  </si>
+  <si>
+    <t>Berge Jaya</t>
+  </si>
+  <si>
+    <t>Berge Neblina</t>
+  </si>
+  <si>
+    <t>Berge Mafadi</t>
+  </si>
+  <si>
+    <t>Berge Logan</t>
+  </si>
+  <si>
+    <t>Berge Blanc</t>
+  </si>
+  <si>
+    <t>Berge Cho Oyu</t>
+  </si>
+  <si>
+    <t>Berge Annapurna</t>
+  </si>
+  <si>
+    <t>Berge K2</t>
+  </si>
+  <si>
+    <t>Berge Makalu</t>
+  </si>
+  <si>
+    <t>Berge Elbrus</t>
+  </si>
+  <si>
+    <t>Berge Kibo</t>
+  </si>
+  <si>
+    <t>Berge Vinson</t>
+  </si>
+  <si>
+    <t>Berge Caubvick</t>
+  </si>
+  <si>
+    <t>Berge Tai Shan</t>
+  </si>
+  <si>
+    <t>Berge Heng Shan</t>
+  </si>
+  <si>
+    <t>Berge Haleakala</t>
+  </si>
+  <si>
+    <t>Berge Hualalai</t>
+  </si>
+  <si>
+    <t>Berge Mauna Kea</t>
+  </si>
+  <si>
+    <t>Berge Mauna Loa</t>
+  </si>
+  <si>
+    <t>Berge Grossglockner</t>
+  </si>
+  <si>
+    <t>Berge Zugspitze</t>
+  </si>
+  <si>
+    <t>Berge Olympus</t>
+  </si>
+  <si>
+    <t>Berge Mulhacen</t>
+  </si>
+  <si>
+    <t>Berge Toubkal</t>
+  </si>
+  <si>
+    <t>Berge Moldoveanu</t>
+  </si>
+  <si>
+    <t>Berge Kenya</t>
+  </si>
+  <si>
+    <t>Berge Meru</t>
+  </si>
+  <si>
+    <t>TBN - Berge Chimborazo</t>
+  </si>
+  <si>
+    <t>TBN - Berge Olympus Mons</t>
+  </si>
+  <si>
+    <t>Berge Dachstein</t>
+  </si>
+  <si>
+    <t>Berge Daisen</t>
+  </si>
+  <si>
+    <t>Berge Kita</t>
+  </si>
+  <si>
+    <t>Berge Lyngor</t>
+  </si>
+  <si>
+    <t>Berge Odel</t>
+  </si>
+  <si>
+    <t>Berge Kuju</t>
+  </si>
+  <si>
+    <t>Berge Dinara</t>
+  </si>
+  <si>
+    <t>Berge Bimberi</t>
+  </si>
+  <si>
+    <t>Berge Sarstein</t>
+  </si>
+  <si>
+    <t>Berge Gasherbrum</t>
+  </si>
+  <si>
+    <t>Berge Ishizuchi</t>
+  </si>
+  <si>
+    <t>Berge McClintock</t>
+  </si>
+  <si>
+    <t>Berge Tsurugi</t>
+  </si>
+  <si>
+    <t>Berge Kosciuszko</t>
+  </si>
+  <si>
+    <t>Berge Mawson</t>
+  </si>
+  <si>
+    <t>Berge Nyangani</t>
+  </si>
+  <si>
+    <t>Berge Nanga Parbat</t>
+  </si>
+  <si>
+    <t>Berge Matterhorn</t>
+  </si>
+  <si>
+    <t>Berge Rosa</t>
+  </si>
+  <si>
+    <t>Berge Atlas</t>
+  </si>
+  <si>
+    <t>Berge Song Shan</t>
+  </si>
+  <si>
+    <t>Berge Stanley</t>
+  </si>
+  <si>
+    <t>Berge Dhaulagiri</t>
+  </si>
+  <si>
+    <t>Berge Bintumani</t>
+  </si>
+  <si>
+    <t>Berge Broad Peak</t>
+  </si>
+  <si>
+    <t>Berge Kinabalu</t>
+  </si>
+  <si>
+    <t>Berge Nimba</t>
+  </si>
+  <si>
+    <t>Berge Torre</t>
+  </si>
+  <si>
+    <t>Berge Hoverla</t>
+  </si>
+  <si>
+    <t>Berge Rinjani</t>
+  </si>
+  <si>
+    <t>Berge Triglav</t>
+  </si>
+  <si>
+    <t>Berge Orizaba</t>
+  </si>
+  <si>
+    <t>Berge Kebnekaise</t>
+  </si>
+  <si>
+    <t>Berge Townsend</t>
+  </si>
+  <si>
+    <t>TBN</t>
+  </si>
+  <si>
+    <t>Berge Tateyama</t>
+  </si>
+  <si>
+    <t>Berge Rysy</t>
+  </si>
+  <si>
+    <t>Berge Catherine</t>
+  </si>
+  <si>
+    <t>Berge Doi Inthanon</t>
+  </si>
+  <si>
+    <t>Berge Namuli</t>
+  </si>
+  <si>
+    <t>Berge Nishikawa</t>
+  </si>
+  <si>
+    <t>Berge Yotei</t>
+  </si>
+  <si>
+    <t>Berge Galdhopiggen</t>
+  </si>
+  <si>
+    <t>Berge Hallasan</t>
+  </si>
+  <si>
+    <t>Berge Ben Nevis</t>
+  </si>
+  <si>
+    <t>Berge Snowdon</t>
+  </si>
+  <si>
+    <t>Berge Snaefell</t>
+  </si>
+  <si>
+    <t>Berge Phan Xi Pang</t>
+  </si>
+  <si>
+    <t>Berge Scafell Pike</t>
+  </si>
+  <si>
+    <t>Berge Jebel Jais</t>
+  </si>
+  <si>
+    <t>Berge Jungfrau</t>
+  </si>
+  <si>
+    <t>Berge Asahidake</t>
+  </si>
+  <si>
+    <t>Berge Annupuri</t>
+  </si>
+  <si>
+    <t>Berge Daisetsu</t>
+  </si>
+  <si>
+    <t>Berge Hakodate</t>
+  </si>
+  <si>
+    <t>Berge Shari</t>
+  </si>
+  <si>
+    <t>Berge Rishiri</t>
+  </si>
+  <si>
+    <t>Isle of Man</t>
+  </si>
+  <si>
+    <t>Liberia</t>
+  </si>
+  <si>
+    <t>TBC</t>
   </si>
   <si>
     <t>Panama</t>
   </si>
   <si>
-    <t>Energy Star</t>
-  </si>
-  <si>
     <t>Marshall Islands</t>
-  </si>
-  <si>
-    <t>Pacific Horizon</t>
-  </si>
-  <si>
-    <t>Liberia</t>
-  </si>
-  <si>
-    <t>Chemical Explorer</t>
-  </si>
-  <si>
-    <t>Hong Kong</t>
-  </si>
-  <si>
-    <t>Atlantic Bridge</t>
-  </si>
-  <si>
-    <t>Auto Prestige</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Deep Diver</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t>India Victory</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Nordic Spirit</t>
-  </si>
-  <si>
-    <t>Bahamas</t>
   </si>
 </sst>
 </file>
@@ -576,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -584,10 +791,9 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,390 +809,1625 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2">
+        <f ca="1">RANDBETWEEN(1111111,9999999)</f>
+        <v>3662670</v>
+      </c>
+      <c r="C2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B66" ca="1" si="0">RANDBETWEEN(1111111,9999999)</f>
+        <v>7222234</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ca="1" si="0"/>
+        <v>1727579</v>
+      </c>
+      <c r="C4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <f t="shared" ca="1" si="0"/>
+        <v>5212608</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <f t="shared" ca="1" si="0"/>
+        <v>8538053</v>
+      </c>
+      <c r="C6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>34</v>
       </c>
-      <c r="B2">
-        <v>9123456</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B7">
+        <f t="shared" ca="1" si="0"/>
+        <v>5110285</v>
+      </c>
+      <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="str">
-        <f>"master."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
-        <v>master.ocpi@keel.com</v>
-      </c>
-      <c r="G2" t="str">
-        <f>"ctodeck."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctodeck.ocpi@keel.com</v>
-      </c>
-      <c r="H2" t="str">
-        <f>"ctoeng."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctoeng.ocpi@keel.com</v>
-      </c>
-      <c r="I2" t="str">
-        <f>"ctoeto."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctoeto.ocpi@keel.com</v>
-      </c>
-      <c r="J2" t="str">
-        <f>"ctocat."&amp;LOWER(LEFT(A2,2)&amp;MID(A2,FIND(" ",A2,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctocat.ocpi@keel.com</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B8">
+        <f t="shared" ca="1" si="0"/>
+        <v>6526986</v>
+      </c>
+      <c r="C8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>36</v>
       </c>
-      <c r="B3">
-        <v>9234567</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B9">
+        <f t="shared" ca="1" si="0"/>
+        <v>7878986</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>37</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="str">
-        <f t="shared" ref="F3:F11" si="0">"master."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
-        <v>master.gltr@keel.com</v>
-      </c>
-      <c r="G3" t="str">
-        <f t="shared" ref="G3:G11" si="1">"ctodeck."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctodeck.gltr@keel.com</v>
-      </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H11" si="2">"ctoeng."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctoeng.gltr@keel.com</v>
-      </c>
-      <c r="I3" t="str">
-        <f t="shared" ref="I3:I11" si="3">"ctoeto."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctoeto.gltr@keel.com</v>
-      </c>
-      <c r="J3" t="str">
-        <f t="shared" ref="J3:J11" si="4">"ctocat."&amp;LOWER(LEFT(A3,2)&amp;MID(A3,FIND(" ",A3,1)+1,2))&amp;"@keel.com"</f>
-        <v>ctocat.gltr@keel.com</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B10">
+        <f t="shared" ca="1" si="0"/>
+        <v>7684259</v>
+      </c>
+      <c r="C10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="B4">
-        <v>9345678</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B11">
+        <f t="shared" ca="1" si="0"/>
+        <v>6864008</v>
+      </c>
+      <c r="C11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="str">
-        <f t="shared" si="0"/>
-        <v>master.enst@keel.com</v>
-      </c>
-      <c r="G4" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.enst@keel.com</v>
-      </c>
-      <c r="H4" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.enst@keel.com</v>
-      </c>
-      <c r="I4" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.enst@keel.com</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.enst@keel.com</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B12">
+        <f t="shared" ca="1" si="0"/>
+        <v>8484517</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B5">
-        <v>9456789</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B13">
+        <f t="shared" ca="1" si="0"/>
+        <v>1676465</v>
+      </c>
+      <c r="C13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="str">
-        <f t="shared" si="0"/>
-        <v>master.paho@keel.com</v>
-      </c>
-      <c r="G5" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.paho@keel.com</v>
-      </c>
-      <c r="H5" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.paho@keel.com</v>
-      </c>
-      <c r="I5" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.paho@keel.com</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.paho@keel.com</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B14">
+        <f t="shared" ca="1" si="0"/>
+        <v>2917487</v>
+      </c>
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>42</v>
       </c>
-      <c r="B6">
-        <v>9567890</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B15">
+        <f t="shared" ca="1" si="0"/>
+        <v>3428271</v>
+      </c>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="str">
-        <f t="shared" si="0"/>
-        <v>master.chex@keel.com</v>
-      </c>
-      <c r="G6" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.chex@keel.com</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.chex@keel.com</v>
-      </c>
-      <c r="I6" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.chex@keel.com</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.chex@keel.com</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B16">
+        <f t="shared" ca="1" si="0"/>
+        <v>1337641</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B7">
-        <v>9678901</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="str">
-        <f t="shared" si="0"/>
-        <v>master.atbr@keel.com</v>
-      </c>
-      <c r="G7" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.atbr@keel.com</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.atbr@keel.com</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.atbr@keel.com</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.atbr@keel.com</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B17">
+        <f t="shared" ca="1" si="0"/>
+        <v>7798258</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>45</v>
       </c>
-      <c r="B8">
-        <v>9789012</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B18">
+        <f t="shared" ca="1" si="0"/>
+        <v>7137552</v>
+      </c>
+      <c r="C18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="str">
-        <f t="shared" si="0"/>
-        <v>master.aupr@keel.com</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.aupr@keel.com</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.aupr@keel.com</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.aupr@keel.com</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.aupr@keel.com</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B19">
+        <f t="shared" ca="1" si="0"/>
+        <v>5739706</v>
+      </c>
+      <c r="C19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>47</v>
       </c>
-      <c r="B9">
-        <v>9890123</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B20">
+        <f t="shared" ca="1" si="0"/>
+        <v>1436433</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" si="0"/>
-        <v>master.dedi@keel.com</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.dedi@keel.com</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.dedi@keel.com</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.dedi@keel.com</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.dedi@keel.com</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B21">
+        <f t="shared" ca="1" si="0"/>
+        <v>1476483</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>49</v>
       </c>
-      <c r="B10">
-        <v>9112233</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B22">
+        <f t="shared" ca="1" si="0"/>
+        <v>3127225</v>
+      </c>
+      <c r="C22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="str">
-        <f t="shared" si="0"/>
-        <v>master.invi@keel.com</v>
-      </c>
-      <c r="G10" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.invi@keel.com</v>
-      </c>
-      <c r="H10" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.invi@keel.com</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.invi@keel.com</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.invi@keel.com</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B23">
+        <f t="shared" ca="1" si="0"/>
+        <v>8157975</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>51</v>
       </c>
-      <c r="B11">
-        <v>9223344</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B24">
+        <f t="shared" ca="1" si="0"/>
+        <v>4491263</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="str">
-        <f t="shared" si="0"/>
-        <v>master.nosp@keel.com</v>
-      </c>
-      <c r="G11" t="str">
-        <f t="shared" si="1"/>
-        <v>ctodeck.nosp@keel.com</v>
-      </c>
-      <c r="H11" t="str">
-        <f t="shared" si="2"/>
-        <v>ctoeng.nosp@keel.com</v>
-      </c>
-      <c r="I11" t="str">
-        <f t="shared" si="3"/>
-        <v>ctoeto.nosp@keel.com</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="4"/>
-        <v>ctocat.nosp@keel.com</v>
+      <c r="B25">
+        <f t="shared" ca="1" si="0"/>
+        <v>4106815</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26">
+        <f t="shared" ca="1" si="0"/>
+        <v>8061363</v>
+      </c>
+      <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27">
+        <f t="shared" ca="1" si="0"/>
+        <v>2674628</v>
+      </c>
+      <c r="C27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ca="1" si="0"/>
+        <v>4489594</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29">
+        <f t="shared" ca="1" si="0"/>
+        <v>6933905</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30">
+        <f t="shared" ca="1" si="0"/>
+        <v>5871329</v>
+      </c>
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31">
+        <f t="shared" ca="1" si="0"/>
+        <v>1396527</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32">
+        <f t="shared" ca="1" si="0"/>
+        <v>9135193</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <f t="shared" ca="1" si="0"/>
+        <v>3332903</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <f t="shared" ca="1" si="0"/>
+        <v>9217837</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35">
+        <f t="shared" ca="1" si="0"/>
+        <v>7297528</v>
+      </c>
+      <c r="C35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36">
+        <f t="shared" ca="1" si="0"/>
+        <v>5315437</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37">
+        <f t="shared" ca="1" si="0"/>
+        <v>1668357</v>
+      </c>
+      <c r="C37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38">
+        <f t="shared" ca="1" si="0"/>
+        <v>8620215</v>
+      </c>
+      <c r="C38" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39">
+        <f t="shared" ca="1" si="0"/>
+        <v>7430384</v>
+      </c>
+      <c r="C39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40">
+        <f t="shared" ca="1" si="0"/>
+        <v>9984866</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41">
+        <f t="shared" ca="1" si="0"/>
+        <v>4302448</v>
+      </c>
+      <c r="C41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42">
+        <f t="shared" ca="1" si="0"/>
+        <v>7513355</v>
+      </c>
+      <c r="C42" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43">
+        <f t="shared" ca="1" si="0"/>
+        <v>4902500</v>
+      </c>
+      <c r="C43" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44">
+        <f t="shared" ca="1" si="0"/>
+        <v>1587416</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45">
+        <f t="shared" ca="1" si="0"/>
+        <v>8836816</v>
+      </c>
+      <c r="C45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46">
+        <f t="shared" ca="1" si="0"/>
+        <v>8530548</v>
+      </c>
+      <c r="C46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47">
+        <f t="shared" ca="1" si="0"/>
+        <v>7749775</v>
+      </c>
+      <c r="C47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48">
+        <f t="shared" ca="1" si="0"/>
+        <v>8944059</v>
+      </c>
+      <c r="C48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49">
+        <f t="shared" ca="1" si="0"/>
+        <v>1712251</v>
+      </c>
+      <c r="C49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50">
+        <f t="shared" ca="1" si="0"/>
+        <v>2359703</v>
+      </c>
+      <c r="C50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51">
+        <f t="shared" ca="1" si="0"/>
+        <v>6816677</v>
+      </c>
+      <c r="C51" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52">
+        <f t="shared" ca="1" si="0"/>
+        <v>1829993</v>
+      </c>
+      <c r="C52" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53">
+        <f t="shared" ca="1" si="0"/>
+        <v>1168842</v>
+      </c>
+      <c r="C53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54">
+        <f t="shared" ca="1" si="0"/>
+        <v>3879831</v>
+      </c>
+      <c r="C54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55">
+        <f t="shared" ca="1" si="0"/>
+        <v>3342869</v>
+      </c>
+      <c r="C55" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>83</v>
+      </c>
+      <c r="B56">
+        <f t="shared" ca="1" si="0"/>
+        <v>7945953</v>
+      </c>
+      <c r="C56" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B57">
+        <f t="shared" ca="1" si="0"/>
+        <v>4445075</v>
+      </c>
+      <c r="C57" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58">
+        <f t="shared" ca="1" si="0"/>
+        <v>4138053</v>
+      </c>
+      <c r="C58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59">
+        <f t="shared" ca="1" si="0"/>
+        <v>9901724</v>
+      </c>
+      <c r="C59" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60">
+        <f t="shared" ca="1" si="0"/>
+        <v>9600338</v>
+      </c>
+      <c r="C60" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61">
+        <f t="shared" ca="1" si="0"/>
+        <v>9249081</v>
+      </c>
+      <c r="C61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62">
+        <f t="shared" ca="1" si="0"/>
+        <v>6969596</v>
+      </c>
+      <c r="C62" t="s">
+        <v>118</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63">
+        <f t="shared" ca="1" si="0"/>
+        <v>1940601</v>
+      </c>
+      <c r="C63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64">
+        <f t="shared" ca="1" si="0"/>
+        <v>7008517</v>
+      </c>
+      <c r="C64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65">
+        <f t="shared" ca="1" si="0"/>
+        <v>9869487</v>
+      </c>
+      <c r="C65" t="s">
+        <v>117</v>
+      </c>
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66">
+        <f t="shared" ca="1" si="0"/>
+        <v>6915507</v>
+      </c>
+      <c r="C66" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>94</v>
+      </c>
+      <c r="B67">
+        <f t="shared" ref="B67:B91" ca="1" si="1">RANDBETWEEN(1111111,9999999)</f>
+        <v>1365359</v>
+      </c>
+      <c r="C67" t="s">
+        <v>119</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68">
+        <f t="shared" ca="1" si="1"/>
+        <v>5517635</v>
+      </c>
+      <c r="C68" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68" t="s">
+        <v>5</v>
+      </c>
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B69">
+        <f t="shared" ca="1" si="1"/>
+        <v>6503388</v>
+      </c>
+      <c r="C69" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70">
+        <f t="shared" ca="1" si="1"/>
+        <v>3716075</v>
+      </c>
+      <c r="C70" t="s">
+        <v>120</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71">
+        <f t="shared" ca="1" si="1"/>
+        <v>5043289</v>
+      </c>
+      <c r="C71" t="s">
+        <v>120</v>
+      </c>
+      <c r="D71" t="s">
+        <v>5</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72">
+        <f t="shared" ca="1" si="1"/>
+        <v>6070842</v>
+      </c>
+      <c r="C72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73">
+        <f t="shared" ca="1" si="1"/>
+        <v>1298352</v>
+      </c>
+      <c r="C73" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74">
+        <f t="shared" ca="1" si="1"/>
+        <v>7607295</v>
+      </c>
+      <c r="C74" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75">
+        <f t="shared" ca="1" si="1"/>
+        <v>1288550</v>
+      </c>
+      <c r="C75" t="s">
+        <v>117</v>
+      </c>
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76">
+        <f t="shared" ca="1" si="1"/>
+        <v>1892297</v>
+      </c>
+      <c r="C76" t="s">
+        <v>119</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77">
+        <f t="shared" ca="1" si="1"/>
+        <v>8954424</v>
+      </c>
+      <c r="C77" t="s">
+        <v>117</v>
+      </c>
+      <c r="D77" t="s">
+        <v>5</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78">
+        <f t="shared" ca="1" si="1"/>
+        <v>2774169</v>
+      </c>
+      <c r="C78" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>104</v>
+      </c>
+      <c r="B79">
+        <f t="shared" ca="1" si="1"/>
+        <v>9736006</v>
+      </c>
+      <c r="C79" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>105</v>
+      </c>
+      <c r="B80">
+        <f t="shared" ca="1" si="1"/>
+        <v>5419153</v>
+      </c>
+      <c r="C80" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" t="s">
+        <v>5</v>
+      </c>
+      <c r="E80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81">
+        <f t="shared" ca="1" si="1"/>
+        <v>9155432</v>
+      </c>
+      <c r="C81" t="s">
+        <v>117</v>
+      </c>
+      <c r="D81" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>107</v>
+      </c>
+      <c r="B82">
+        <f t="shared" ca="1" si="1"/>
+        <v>7115772</v>
+      </c>
+      <c r="C82" t="s">
+        <v>117</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83">
+        <f t="shared" ca="1" si="1"/>
+        <v>5056392</v>
+      </c>
+      <c r="C83" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>109</v>
+      </c>
+      <c r="B84">
+        <f t="shared" ca="1" si="1"/>
+        <v>9940636</v>
+      </c>
+      <c r="C84" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>110</v>
+      </c>
+      <c r="B85">
+        <f t="shared" ca="1" si="1"/>
+        <v>5307953</v>
+      </c>
+      <c r="C85" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>111</v>
+      </c>
+      <c r="B86">
+        <f t="shared" ca="1" si="1"/>
+        <v>4604058</v>
+      </c>
+      <c r="C86" t="s">
+        <v>117</v>
+      </c>
+      <c r="D86" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87">
+        <f t="shared" ca="1" si="1"/>
+        <v>7833047</v>
+      </c>
+      <c r="C87" t="s">
+        <v>117</v>
+      </c>
+      <c r="D87" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>113</v>
+      </c>
+      <c r="B88">
+        <f t="shared" ca="1" si="1"/>
+        <v>3755295</v>
+      </c>
+      <c r="C88" t="s">
+        <v>117</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>114</v>
+      </c>
+      <c r="B89">
+        <f t="shared" ca="1" si="1"/>
+        <v>6359642</v>
+      </c>
+      <c r="C89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D89" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90">
+        <f t="shared" ca="1" si="1"/>
+        <v>2854652</v>
+      </c>
+      <c r="C90" t="s">
+        <v>117</v>
+      </c>
+      <c r="D90" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91">
+        <f t="shared" ca="1" si="1"/>
+        <v>7681024</v>
+      </c>
+      <c r="C91" t="s">
+        <v>117</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -995,13 +2436,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select a valid Classification Society from the provided list." xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Reference!$A$1:$A$13</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select a valid Vessel Type from the provided list." xr:uid="{00000000-0002-0000-0000-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>Reference!$B$1:$B$12</xm:f>
           </x14:formula1>
@@ -1020,103 +2461,103 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
